--- a/astro-site/public/dl/guia-chocolateria-obrador/sensibilidad-al-precio-del-cacao.xlsx
+++ b/astro-site/public/dl/guia-chocolateria-obrador/sensibilidad-al-precio-del-cacao.xlsx
@@ -792,7 +792,7 @@
     <row r="28" ht="70" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>Todo lo que ves relleno es la bombonería «La Almendra», el caso de ejemplo de la guía: 75 m2, obrador y tienda, 28 referencias. Los precios de las coberturas negra y de origen están verificados con su tienda y su fecha; los de leche y blanca son supuestos declarados, porque no hay precio público verificado. Todos los gramajes, el mix y el volumen son supuestos: sustitúyelos por los tuyos en cuanto tengas dos semanas de TPV.</t>
+          <t>Todo lo que ves relleno es la bombonería «La Almendra», el caso de ejemplo de la guía: 75 m², obrador y tienda, 28 referencias. Los precios de las coberturas negra y de origen están verificados con su tienda y su fecha; los de leche y blanca son supuestos declarados, porque no hay precio público verificado. Todos los gramajes, el mix y el volumen son supuestos: sustitúyelos por los tuyos en cuanto tengas dos semanas de TPV.</t>
         </is>
       </c>
     </row>
@@ -987,7 +987,7 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>REGLA UNICA de la casa, y es SUPUESTO: no existe dato publico de food cost de bomboneria. `margen_bruto_objetivo()` deriva el margen sobre PVP, que con este food cost es el 70 %. El libro 4 pide UNO de los dos numeros y calcula el otro: margen bruto y food cost son la misma regla dicha dos veces, y publicarlos como dos reglas es un error de metodo prohibido. Se calcula SIEMPRE sobre base imponible en los DOS lados del cociente (regla 3 de §2.3).</t>
+          <t>REGLA ÚNICA de la casa, y es SUPUESTO: no existe dato publico de food cost de bombonería. `margen_bruto_objetivo()` deriva el margen sobre PVP, que con este food cost es el 70 %. El libro 4 pide UNO de los dos números y calcula el otro: margen bruto y food cost son la misma regla dicha dos veces, y publicarlos como dos reglas es un error de método prohibido. Se calcula SIEMPRE sobre base imponible en los DOS lados del cociente (regla 3 de §2.3).</t>
         </is>
       </c>
     </row>
@@ -1063,7 +1063,7 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>Clientes por dia en velocidad de crucero. NO es un dato del sector: `N-13` prohibe publicar un ticket medio de chocolateria o un reparto mensual de ventas como dato, porque no existe dato publico. La guia ensena a medirlo con el TPV en dos semanas. Esta calibrado para que el margen neto del ano de crucero caiga entre el 9 % y el 11 %: por encima, el caso se lee como optimista y un refutador lo tumba con razon. Es la UNICA palanca que se toca para mover el margen; los costes no se maquillan.</t>
+          <t>Clientes por día en velocidad de crucero. NO es un dato del sector: `N-13` prohíbe publicar un ticket medio de chocolatería o un reparto mensual de ventas como dato, porque no existe dato publico. La guía enseña a medirlo con el TPV en dos semanas. Esta calibrado para que el margen neto del año de crucero caiga entre el 9 % y el 11 %: por encima, el caso se lee como optimista y un refutador lo tumba con razón. Es la ÚNICA palanca que se toca para mover el margen; los costes no se maquillan.</t>
         </is>
       </c>
     </row>
@@ -1088,7 +1088,7 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>De aqui sale el ticket medio, que NO se teclea: se calcula como PVP medio ponderado de la carta x piezas por ticket. En bomboneria es BAJO -1,4- porque la unidad de venta real es la caja, no la pieza: quien entra a por un regalo se lleva UNA caja de 20 euros, no ocho bombones sueltos.</t>
+          <t>De aquí sale el ticket medio, que NO se teclea: se calcula como PVP medio ponderado de la carta x piezas por ticket. En bombonería es BAJO -1,4- porque la unidad de venta real es la caja, no la pieza: quien entra a por un regalo se lleva UNA caja de 20 euros, no ocho bombones sueltos.</t>
         </is>
       </c>
     </row>
@@ -1113,7 +1113,7 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>6 dias por semana x 52 semanas = 312, menos 8 dias de cierre por festivos = 304. En agosto la TIENDA NO CIERRA: lo que para es el obrador (D36, y el literal del kit dice «la tienda abre para el turista aunque el obrador pare»). Una bomboneria de menos de 300 m2 tiene libertad horaria por el art. 5.2 de la Ley 1/2004, no por el 5.1 (`CHN-77`).</t>
+          <t>6 días por semana x 52 semanas = 312, menos 8 días de cierre por festivos = 304. En agosto la TIENDA NO CIERRA: lo que para es el obrador (D36, y el literal del kit dice «la tienda abre para el turista aunque el obrador pare»). Una bombonería de menos de 300 m² tiene libertad horaria por el art. 5.2 de la Ley 1/2004, no por el 5.1 (`CHN-77`).</t>
         </is>
       </c>
     </row>
@@ -1515,7 +1515,7 @@
       </c>
       <c r="J8" s="5" t="inlineStr">
         <is>
-          <t>Factor 1,5 frente a la de marca, y es la decision de posicionamiento mas cara del negocio (decision 5 del bonus 2). La pagina no declara si el precio lleva IVA: se trata como base imponible y se marca.</t>
+          <t>Factor 1,5 frente a la de marca, y es la decisión de posicionamiento mas cara del negocio (decisión 5 del bonus 2). La pagina no declara si el precio lleva IVA: se trata como base imponible y se marca.</t>
         </is>
       </c>
     </row>
@@ -1609,7 +1609,7 @@
       </c>
       <c r="J10" s="5" t="inlineStr">
         <is>
-          <t>SUPUESTO declarado. Ojo al chocolate blanco: NO lleva materia seca desgrasada de cacao, y por eso el art. 6.d) del RD 1055/2003 NO le obliga a la mencion «cacao: X % minimo» (`CHN-07`).</t>
+          <t>SUPUESTO declarado. Ojo al chocolate blanco: NO lleva materia seca desgrasada de cacao, y por eso el art. 6.d) del RD 1055/2003 NO le obliga a la mención «cacao: X % mínimo» (`CHN-07`).</t>
         </is>
       </c>
     </row>
@@ -1750,12 +1750,12 @@
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>Bombon de ganache de chocolate negro 70 %</t>
+          <t>Bombón de ganache de chocolate negro 70 %</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Bombones de coleccion</t>
+          <t>Bombones de colección</t>
         </is>
       </c>
       <c r="D16" s="14" t="inlineStr">
@@ -1833,12 +1833,12 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>Bombon de ganache de leche y vainilla</t>
+          <t>Bombón de ganache de leche y vainilla</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Bombones de coleccion</t>
+          <t>Bombones de colección</t>
         </is>
       </c>
       <c r="D17" s="14" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>Bombon de praline de avellana</t>
+          <t>Bombón de praline de avellana</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Bombones de coleccion</t>
+          <t>Bombones de colección</t>
         </is>
       </c>
       <c r="D18" s="14" t="inlineStr">
@@ -1999,12 +1999,12 @@
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>Bombon de gianduja de avellana</t>
+          <t>Bombón de gianduja de avellana</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Bombones de coleccion</t>
+          <t>Bombones de colección</t>
         </is>
       </c>
       <c r="D19" s="14" t="inlineStr">
@@ -2087,7 +2087,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Bombones de coleccion</t>
+          <t>Bombones de colección</t>
         </is>
       </c>
       <c r="D20" s="14" t="inlineStr">
@@ -2165,12 +2165,12 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>Bombon de licor de ron</t>
+          <t>Bombón de licor de ron</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Bombones de coleccion</t>
+          <t>Bombones de colección</t>
         </is>
       </c>
       <c r="D21" s="14" t="inlineStr">
@@ -2248,12 +2248,12 @@
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>Bombon de caramelo salado</t>
+          <t>Bombón de caramelo salado</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Bombones de coleccion</t>
+          <t>Bombones de colección</t>
         </is>
       </c>
       <c r="D22" s="14" t="inlineStr">
@@ -2331,12 +2331,12 @@
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>Bombon de praline de cacahuete</t>
+          <t>Bombón de praline de cacahuete</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Bombones de coleccion</t>
+          <t>Bombones de colección</t>
         </is>
       </c>
       <c r="D23" s="14" t="inlineStr">
@@ -2414,12 +2414,12 @@
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>Bombon crujiente de sesamo y barquillo</t>
+          <t>Bombón crujiente de sesamo y barquillo</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Bombones de coleccion</t>
+          <t>Bombones de colección</t>
         </is>
       </c>
       <c r="D24" s="14" t="inlineStr">
@@ -2497,12 +2497,12 @@
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>Bombon de naranja confitada y chocolate negro</t>
+          <t>Bombón de naranja confitada y chocolate negro</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Bombones de coleccion</t>
+          <t>Bombones de colección</t>
         </is>
       </c>
       <c r="D25" s="14" t="inlineStr">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>Turron de chocolate con almendra, 250 g</t>
+          <t>Turrón de chocolate con almendra, 250 g</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -4718,7 +4718,7 @@
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>Bombon de ganache de chocolate negro 70 %</t>
+          <t>Bombón de ganache de chocolate negro 70 %</t>
         </is>
       </c>
       <c r="C16" s="16">
@@ -4793,7 +4793,7 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>Bombon de ganache de leche y vainilla</t>
+          <t>Bombón de ganache de leche y vainilla</t>
         </is>
       </c>
       <c r="C17" s="16">
@@ -4868,7 +4868,7 @@
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>Bombon de praline de avellana</t>
+          <t>Bombón de praline de avellana</t>
         </is>
       </c>
       <c r="C18" s="16">
@@ -4943,7 +4943,7 @@
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>Bombon de gianduja de avellana</t>
+          <t>Bombón de gianduja de avellana</t>
         </is>
       </c>
       <c r="C19" s="16">
@@ -5093,7 +5093,7 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>Bombon de licor de ron</t>
+          <t>Bombón de licor de ron</t>
         </is>
       </c>
       <c r="C21" s="16">
@@ -5168,7 +5168,7 @@
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>Bombon de caramelo salado</t>
+          <t>Bombón de caramelo salado</t>
         </is>
       </c>
       <c r="C22" s="16">
@@ -5243,7 +5243,7 @@
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>Bombon de praline de cacahuete</t>
+          <t>Bombón de praline de cacahuete</t>
         </is>
       </c>
       <c r="C23" s="16">
@@ -5318,7 +5318,7 @@
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>Bombon crujiente de sesamo y barquillo</t>
+          <t>Bombón crujiente de sesamo y barquillo</t>
         </is>
       </c>
       <c r="C24" s="16">
@@ -5393,7 +5393,7 @@
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>Bombon de naranja confitada y chocolate negro</t>
+          <t>Bombón de naranja confitada y chocolate negro</t>
         </is>
       </c>
       <c r="C25" s="16">
@@ -6368,7 +6368,7 @@
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>Turron de chocolate con almendra, 250 g</t>
+          <t>Turrón de chocolate con almendra, 250 g</t>
         </is>
       </c>
       <c r="C38" s="16">
@@ -7081,7 +7081,7 @@
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>Bombon de ganache de chocolate negro 70 %</t>
+          <t>Bombón de ganache de chocolate negro 70 %</t>
         </is>
       </c>
       <c r="C16" s="16">
@@ -7157,7 +7157,7 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>Bombon de ganache de leche y vainilla</t>
+          <t>Bombón de ganache de leche y vainilla</t>
         </is>
       </c>
       <c r="C17" s="16">
@@ -7233,7 +7233,7 @@
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>Bombon de praline de avellana</t>
+          <t>Bombón de praline de avellana</t>
         </is>
       </c>
       <c r="C18" s="16">
@@ -7309,7 +7309,7 @@
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>Bombon de gianduja de avellana</t>
+          <t>Bombón de gianduja de avellana</t>
         </is>
       </c>
       <c r="C19" s="16">
@@ -7461,7 +7461,7 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>Bombon de licor de ron</t>
+          <t>Bombón de licor de ron</t>
         </is>
       </c>
       <c r="C21" s="16">
@@ -7537,7 +7537,7 @@
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>Bombon de caramelo salado</t>
+          <t>Bombón de caramelo salado</t>
         </is>
       </c>
       <c r="C22" s="16">
@@ -7613,7 +7613,7 @@
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>Bombon de praline de cacahuete</t>
+          <t>Bombón de praline de cacahuete</t>
         </is>
       </c>
       <c r="C23" s="16">
@@ -7689,7 +7689,7 @@
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>Bombon crujiente de sesamo y barquillo</t>
+          <t>Bombón crujiente de sesamo y barquillo</t>
         </is>
       </c>
       <c r="C24" s="16">
@@ -7765,7 +7765,7 @@
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>Bombon de naranja confitada y chocolate negro</t>
+          <t>Bombón de naranja confitada y chocolate negro</t>
         </is>
       </c>
       <c r="C25" s="16">
@@ -8753,7 +8753,7 @@
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>Turron de chocolate con almendra, 250 g</t>
+          <t>Turrón de chocolate con almendra, 250 g</t>
         </is>
       </c>
       <c r="C38" s="16">

--- a/astro-site/public/dl/guia-chocolateria-obrador/sensibilidad-al-precio-del-cacao.xlsx
+++ b/astro-site/public/dl/guia-chocolateria-obrador/sensibilidad-al-precio-del-cacao.xlsx
@@ -1916,7 +1916,7 @@
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>Bombón de praline de avellana</t>
+          <t>Bombón de praliné de avellana</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2331,7 +2331,7 @@
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>Bombón de praline de cacahuete</t>
+          <t>Bombón de praliné de cacahuete</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2414,7 +2414,7 @@
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>Bombón crujiente de sesamo y barquillo</t>
+          <t>Bombón crujiente de sésamo y barquillo</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2995,7 +2995,7 @@
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>Tableta rellena de praline, 100 g</t>
+          <t>Tableta rellena de praliné, 100 g</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -3493,7 +3493,7 @@
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>Hueso de santo banado en chocolate</t>
+          <t>Hueso de santo bañado en chocolate</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -3659,7 +3659,7 @@
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>Almendras marcona banadas en chocolate, bolsa de 150 g</t>
+          <t>Almendras marcona bañadas en chocolate, bolsa de 150 g</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -4868,7 +4868,7 @@
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>Bombón de praline de avellana</t>
+          <t>Bombón de praliné de avellana</t>
         </is>
       </c>
       <c r="C18" s="16">
@@ -5243,7 +5243,7 @@
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>Bombón de praline de cacahuete</t>
+          <t>Bombón de praliné de cacahuete</t>
         </is>
       </c>
       <c r="C23" s="16">
@@ -5318,7 +5318,7 @@
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>Bombón crujiente de sesamo y barquillo</t>
+          <t>Bombón crujiente de sésamo y barquillo</t>
         </is>
       </c>
       <c r="C24" s="16">
@@ -5843,7 +5843,7 @@
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>Tableta rellena de praline, 100 g</t>
+          <t>Tableta rellena de praliné, 100 g</t>
         </is>
       </c>
       <c r="C31" s="16">
@@ -6293,7 +6293,7 @@
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>Hueso de santo banado en chocolate</t>
+          <t>Hueso de santo bañado en chocolate</t>
         </is>
       </c>
       <c r="C37" s="16">
@@ -6443,7 +6443,7 @@
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>Almendras marcona banadas en chocolate, bolsa de 150 g</t>
+          <t>Almendras marcona bañadas en chocolate, bolsa de 150 g</t>
         </is>
       </c>
       <c r="C39" s="16">
@@ -7233,7 +7233,7 @@
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>Bombón de praline de avellana</t>
+          <t>Bombón de praliné de avellana</t>
         </is>
       </c>
       <c r="C18" s="16">
@@ -7613,7 +7613,7 @@
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>Bombón de praline de cacahuete</t>
+          <t>Bombón de praliné de cacahuete</t>
         </is>
       </c>
       <c r="C23" s="16">
@@ -7689,7 +7689,7 @@
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>Bombón crujiente de sesamo y barquillo</t>
+          <t>Bombón crujiente de sésamo y barquillo</t>
         </is>
       </c>
       <c r="C24" s="16">
@@ -8221,7 +8221,7 @@
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>Tableta rellena de praline, 100 g</t>
+          <t>Tableta rellena de praliné, 100 g</t>
         </is>
       </c>
       <c r="C31" s="16">
@@ -8677,7 +8677,7 @@
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>Hueso de santo banado en chocolate</t>
+          <t>Hueso de santo bañado en chocolate</t>
         </is>
       </c>
       <c r="C37" s="16">
@@ -8829,7 +8829,7 @@
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>Almendras marcona banadas en chocolate, bolsa de 150 g</t>
+          <t>Almendras marcona bañadas en chocolate, bolsa de 150 g</t>
         </is>
       </c>
       <c r="C39" s="16">
